--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484139_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484139_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0995</v>
+        <v>4.2904</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2677</v>
+        <v>3.3769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8318</v>
+        <v>0.9135</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5624</v>
+        <v>0.2507</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6503</v>
+        <v>0.2572</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9121</v>
+        <v>-0.0065</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0035</v>
+        <v>0.6837</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2405</v>
+        <v>0.0361</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7631</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4412</v>
+        <v>-0.433</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.2212</v>
       </c>
       <c r="O2" t="n">
-        <v>0.149</v>
+        <v>-0.6542</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3306</v>
+        <v>0.5753</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0496</v>
+        <v>0.3515</v>
       </c>
       <c r="U2" t="n">
-        <v>0.281</v>
+        <v>0.2238</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2065</v>
+        <v>2.0757</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2065</v>
+        <v>2.3417</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6516</v>
+        <v>3.8968</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9065</v>
+        <v>3.2894</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7452</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2507</v>
+        <v>1.5624</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2572</v>
+        <v>0.6503</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0065</v>
+        <v>0.9121</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6837</v>
+        <v>2.0035</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0361</v>
+        <v>1.2405</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.7631</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.433</v>
+        <v>-0.4412</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2212</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6542</v>
+        <v>0.149</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0635</v>
+        <v>1.128</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1189</v>
+        <v>1.0714</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0555</v>
+        <v>0.0566</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0757</v>
+        <v>1.2065</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3417</v>
+        <v>1.2065</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2033</v>
+        <v>3.5718</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7368</v>
+        <v>2.1052</v>
       </c>
       <c r="F4" t="n">
         <v>1.4665</v>
@@ -766,10 +766,10 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2834</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4024</v>
+        <v>-0.0339</v>
       </c>
       <c r="U4" t="n">
         <v>0.1189</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0965</v>
+        <v>3.5262</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1904</v>
+        <v>1.069</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9061</v>
+        <v>2.4572</v>
       </c>
       <c r="G5" t="n">
         <v>2.3129</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5374</v>
+        <v>-0.1077</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6121</v>
+        <v>0.2665</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0747</v>
+        <v>-0.3742</v>
       </c>
       <c r="V5" t="n">
         <v>-0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6796</v>
+        <v>3.1081</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4553</v>
+        <v>1.6594</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2242</v>
+        <v>1.4487</v>
       </c>
       <c r="G6" t="n">
         <v>1.6457</v>
@@ -922,13 +922,13 @@
         <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.2041</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>-0.034</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3945</v>
+        <v>-0.1701</v>
       </c>
       <c r="V6" t="n">
         <v>0.6745</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. COLL JANER</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0262</v>
+        <v>2.4142</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9534</v>
+        <v>2.0074</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0727</v>
+        <v>0.4069</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2701</v>
+        <v>0.2342</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.111</v>
+        <v>0.8511</v>
       </c>
       <c r="I7" t="n">
-        <v>1.381</v>
+        <v>-0.6168</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2652</v>
+        <v>0.9263</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>1.8347</v>
       </c>
       <c r="L7" t="n">
-        <v>1.245</v>
+        <v>-0.9084</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0049</v>
+        <v>-0.6921</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1312</v>
+        <v>-0.9837</v>
       </c>
       <c r="O7" t="n">
-        <v>0.136</v>
+        <v>0.2916</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7935</v>
+        <v>2.9758</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0374</v>
+        <v>-0.0184</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3117</v>
+        <v>0.652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2743</v>
+        <v>-0.6704</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>M. COLL JANER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7769</v>
+        <v>2.2365</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6786</v>
+        <v>1.2198</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0983</v>
+        <v>1.0166</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2342</v>
+        <v>1.2701</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8511</v>
+        <v>-0.111</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6168</v>
+        <v>1.381</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9263</v>
+        <v>1.2652</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8347</v>
+        <v>0.0202</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9084</v>
+        <v>1.245</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6921</v>
+        <v>0.0049</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9837</v>
+        <v>-0.1312</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2916</v>
+        <v>0.136</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9758</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.1729</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3232</v>
+        <v>-0.0453</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.979</v>
+        <v>0.2182</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4694</v>
+        <v>0.3968</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5590000000000001</v>
+        <v>-0.4715</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9105</v>
+        <v>0.8683</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3064</v>
+        <v>-0.6253</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>-0.8818</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1336</v>
+        <v>0.2565</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8657</v>
+        <v>0.0159</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3451</v>
+        <v>-0.6293</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4794</v>
+        <v>0.6451</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5593</v>
+        <v>-0.6412</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0949</v>
+        <v>-0.2525</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6542</v>
+        <v>-0.3886</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>1.5871</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9758</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3812</v>
+        <v>-0.299</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4148</v>
+        <v>-0.4874</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0336</v>
+        <v>0.1884</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2182</v>
+        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7458</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3257</v>
+        <v>-0.0829</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2901</v>
+        <v>-0.9091</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6158</v>
+        <v>0.8263</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6253</v>
+        <v>1.3064</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8818</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2565</v>
+        <v>-1.1336</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0159</v>
+        <v>1.8657</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6293</v>
+        <v>2.3451</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6451</v>
+        <v>-0.4794</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6412</v>
+        <v>-0.5593</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2525</v>
+        <v>0.0949</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3886</v>
+        <v>-0.6542</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5871</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5871</v>
+        <v>2.9758</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3701</v>
+        <v>0.829</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.306</v>
+        <v>0.9467</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0641</v>
+        <v>-0.1177</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.266</v>
+        <v>-2.2182</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7458</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9273</v>
+        <v>-1.3074</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1438</v>
+        <v>-3.3276</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2166</v>
+        <v>2.0202</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0707</v>
@@ -1312,13 +1312,13 @@
         <v>2.9758</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1354</v>
+        <v>0.7553</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2041</v>
+        <v>1.0204</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0687</v>
+        <v>-0.2651</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2521</v>
+        <v>-3.2777</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7054</v>
+        <v>-0.7871</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5467</v>
+        <v>-2.4906</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7377</v>
@@ -1390,13 +1390,13 @@
         <v>0.7935</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9149</v>
+        <v>0.0595</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4874</v>
+        <v>0.4309</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4275</v>
+        <v>-0.3713</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4012</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.1493</v>
+        <v>18.7728</v>
       </c>
       <c r="E13" t="n">
-        <v>8.608399999999996</v>
+        <v>9.231799999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>9.541</v>
+        <v>9.540999999999997</v>
       </c>
       <c r="G13" t="n">
         <v>8.0161</v>
@@ -1438,16 +1438,16 @@
         <v>4.712599999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3035</v>
+        <v>3.303500000000001</v>
       </c>
       <c r="J13" t="n">
         <v>13.0182</v>
       </c>
       <c r="K13" t="n">
-        <v>7.1892</v>
+        <v>7.189199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>5.829200000000001</v>
+        <v>5.8292</v>
       </c>
       <c r="M13" t="n">
         <v>-5.0024</v>
@@ -1459,7 +1459,7 @@
         <v>-2.5258</v>
       </c>
       <c r="P13" t="n">
-        <v>4.9596</v>
+        <v>4.959599999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.8788</v>
@@ -1468,13 +1468,13 @@
         <v>19.8385</v>
       </c>
       <c r="S13" t="n">
-        <v>2.352200000000001</v>
+        <v>2.9758</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5152</v>
+        <v>4.1388</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.163</v>
+        <v>-1.1629</v>
       </c>
       <c r="V13" t="n">
         <v>2.821499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7415</v>
+        <v>5.8613</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3779</v>
+        <v>5.3981</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3637</v>
+        <v>0.4632</v>
       </c>
       <c r="G14" t="n">
         <v>4.0094</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0901</v>
+        <v>0.0297</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4226</v>
+        <v>-0.4023</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3325</v>
+        <v>0.432</v>
       </c>
       <c r="V14" t="n">
         <v>3.2109</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,75 +1579,71 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4541</v>
+        <v>1.6004</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2076</v>
+        <v>0.3924</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2465</v>
+        <v>1.208</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2211</v>
+        <v>-0.3792</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0806</v>
+        <v>-0.1668</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3018</v>
+        <v>-0.2124</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4135</v>
+        <v>0.2619</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3332</v>
+        <v>0.2218</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0803</v>
+        <v>0.0402</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6347</v>
+        <v>-0.6412</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2525</v>
+        <v>-0.3886</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3821</v>
+        <v>-0.2526</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7855</v>
+        <v>2.1822</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9537</v>
+        <v>-0.2026</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5281</v>
+        <v>0.1304</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4256</v>
+        <v>-0.3331</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0639</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P. MULIO CAMPOS</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1657,71 +1653,75 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5195</v>
+        <v>1.6004</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3699</v>
+        <v>0.3924</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8502999999999999</v>
+        <v>1.208</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5862</v>
+        <v>-0.3792</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3583</v>
+        <v>-0.1668</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7721</v>
+        <v>-0.2124</v>
       </c>
       <c r="J16" t="n">
-        <v>2.424</v>
+        <v>0.2619</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9436</v>
+        <v>0.2218</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5195</v>
+        <v>0.0402</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8379</v>
+        <v>-0.6412</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5853</v>
+        <v>-0.3886</v>
       </c>
       <c r="O16" t="n">
         <v>-0.2526</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>2.1822</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4852</v>
+        <v>-0.2026</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6122</v>
+        <v>0.1304</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1271</v>
+        <v>-0.3331</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1469</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B. GASSAMA KARGBO</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1731,73 +1731,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3956</v>
+        <v>1.3209</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4239</v>
+        <v>1.167</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8195</v>
+        <v>0.1538</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3792</v>
+        <v>-0.2211</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1668</v>
+        <v>0.0806</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2124</v>
+        <v>-0.3018</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2619</v>
+        <v>0.4135</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2218</v>
+        <v>0.3332</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0402</v>
+        <v>0.0803</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6412</v>
+        <v>-0.6347</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3886</v>
+        <v>-0.2525</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2526</v>
+        <v>-0.3821</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4074</v>
+        <v>0.8205</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6858</v>
+        <v>0.4876</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7216</v>
+        <v>0.3329</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0639</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.3299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,67 +1809,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3956</v>
+        <v>0.3291</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4239</v>
+        <v>1.2678</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8195</v>
+        <v>-0.9387</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3792</v>
+        <v>1.5862</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1668</v>
+        <v>2.3583</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2124</v>
+        <v>-0.7721</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2619</v>
+        <v>2.424</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2218</v>
+        <v>2.9436</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>-0.5195</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6412</v>
+        <v>-0.8379</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3886</v>
+        <v>-0.5853</v>
       </c>
       <c r="O18" t="n">
         <v>-0.2526</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1822</v>
+        <v>0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4074</v>
+        <v>0.2947</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6858</v>
+        <v>0.5102</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7216</v>
+        <v>-0.2155</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.1469</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="19">
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2076</v>
+        <v>-0.0197</v>
       </c>
       <c r="E19" t="n">
         <v>0.3529</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5605</v>
+        <v>-0.3726</v>
       </c>
       <c r="G19" t="n">
         <v>1.6534</v>
@@ -1932,13 +1932,13 @@
         <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4642</v>
+        <v>-0.2763</v>
       </c>
       <c r="T19" t="n">
         <v>-0.6235000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1592</v>
+        <v>0.3471</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6032</v>
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3342</v>
+        <v>-1.7456</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-1.995</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4364</v>
+        <v>0.2494</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3594</v>
@@ -2010,13 +2010,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.477</v>
+        <v>1.0656</v>
       </c>
       <c r="T20" t="n">
-        <v>2.0406</v>
+        <v>0.8162</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4364</v>
+        <v>0.2494</v>
       </c>
       <c r="V20" t="n">
         <v>0.532</v>
@@ -2043,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5432</v>
+        <v>-3.6624</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1978</v>
+        <v>-2.7897</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3454</v>
+        <v>-0.8727</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4113</v>
@@ -2088,13 +2088,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7594</v>
+        <v>-0.8786</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3797</v>
+        <v>0.0284</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3797</v>
+        <v>-0.907</v>
       </c>
       <c r="V21" t="n">
         <v>1.2065</v>
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8764</v>
+        <v>-3.8698</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0133</v>
+        <v>-1.5031</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8632</v>
+        <v>-2.3667</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7176</v>
@@ -2166,13 +2166,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7459</v>
+        <v>0.2608</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4874</v>
+        <v>0.0227</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2585</v>
+        <v>0.238</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4129</v>
@@ -2187,7 +2187,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,73 +2199,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0477</v>
+        <v>-4.1052</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7574</v>
+        <v>-2.4178</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2903</v>
+        <v>-1.6875</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3227</v>
+        <v>-4.6144</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0987</v>
+        <v>-2.7876</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.224</v>
+        <v>-1.8268</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3612</v>
+        <v>-2.5142</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3216</v>
+        <v>-1.1991</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6827</v>
+        <v>-1.3151</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6839</v>
+        <v>-2.1002</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7772</v>
+        <v>-1.5885</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.5117</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7774</v>
+        <v>1.1903</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.9596</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.539</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2495</v>
+        <v>0.0965</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7886</v>
+        <v>-0.8489</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4085</v>
+        <v>0.0713</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,67 +2277,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2658</v>
+        <v>-4.8615</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.438</v>
+        <v>-5.0635</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8278</v>
+        <v>0.202</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6144</v>
+        <v>-1.3227</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7876</v>
+        <v>-1.0987</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8268</v>
+        <v>-0.224</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.5142</v>
+        <v>0.3612</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1991</v>
+        <v>-0.3216</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3151</v>
+        <v>0.6827</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1002</v>
+        <v>-1.6839</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5885</v>
+        <v>-0.7772</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5117</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1903</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-4.9596</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.913</v>
+        <v>-0.3528</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9238</v>
+        <v>-0.0566</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9892</v>
+        <v>-0.2963</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0713</v>
+        <v>-0.4085</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9851</v>
+        <v>-6.5566</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2482</v>
+        <v>-4.0441</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7369</v>
+        <v>-2.5124</v>
       </c>
       <c r="G25" t="n">
         <v>-4.2392</v>
@@ -2400,13 +2400,13 @@
         <v>0.7935</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3491</v>
+        <v>0.0794</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2551</v>
+        <v>0.4592</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.3798</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2065</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.7537</v>
+        <v>-14.1087</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.9649</v>
+        <v>-8.842599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.7888</v>
+        <v>-5.2662</v>
       </c>
       <c r="G26" t="n">
         <v>-8.395099999999999</v>
@@ -2451,7 +2451,7 @@
         <v>-3.5158</v>
       </c>
       <c r="J26" t="n">
-        <v>5.264100000000002</v>
+        <v>5.264099999999998</v>
       </c>
       <c r="K26" t="n">
         <v>2.698300000000001</v>
@@ -2466,7 +2466,7 @@
         <v>-7.577599999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.081900000000001</v>
+        <v>-6.0819</v>
       </c>
       <c r="P26" t="n">
         <v>-2.7773</v>
@@ -2478,19 +2478,19 @@
         <v>17.061</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.7596</v>
+        <v>-0.1146999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4769</v>
+        <v>1.5992</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.236899999999999</v>
+        <v>-1.7143</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.8212</v>
+        <v>-2.821199999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>4.1324</v>
+        <v>4.132400000000001</v>
       </c>
       <c r="X26" t="n">
         <v>-6.953600000000001</v>
